--- a/signal_android_buttons.xlsx
+++ b/signal_android_buttons.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Buttons" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Buttons'!$A$1:$B$545</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Buttons'!$A$1:$C$545</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,11 +450,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B545"/>
+  <dimension ref="A1:C545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,11 @@
           <t>interface</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -480,6 +486,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>open search for chats, contacts, and messages</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -492,6 +503,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>open the chats overflow menu</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -504,6 +520,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>open or toggle the active notification profile</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,6 +537,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>open proxy status</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -528,6 +554,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>start creating a group</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -540,6 +571,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>lock the app with the passphrase</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -552,6 +588,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>clear unread on every chat</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -564,6 +605,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>share an invite to Signal</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -576,6 +622,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>show only unread chats</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -588,6 +639,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>show all chats again</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -600,6 +656,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>open starred messages</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -612,6 +673,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>manage notification profiles</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -624,6 +690,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>start a new conversation</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -636,6 +707,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>open the camera to send media</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -648,6 +724,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>stay on or return to the chats list</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -660,6 +741,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>open the call log</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -672,6 +758,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>open stories</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -684,6 +775,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>open settings</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -696,6 +792,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>open your profile</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -708,6 +809,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>open that chat</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -720,6 +826,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>filter chats by folder</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -732,6 +843,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>leave search and show the full list</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -744,6 +860,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>empty the search field</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -756,6 +877,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>narrow search by type</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -768,6 +894,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>cancel multi-select</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -780,6 +911,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>pin selected chats</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -792,6 +928,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>archive selected chats</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -804,6 +945,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>delete selected chats</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -816,6 +962,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>mute selected chats</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -828,6 +979,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>mark selected chats read</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -840,6 +996,11 @@
           <t>chats</t>
         </is>
       </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>select every visible chat</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -852,6 +1013,11 @@
           <t>archive</t>
         </is>
       </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>search archived chats</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -864,6 +1030,11 @@
           <t>archive</t>
         </is>
       </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>return to the main chat list</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -876,6 +1047,11 @@
           <t>archive</t>
         </is>
       </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>start a new conversation</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -888,6 +1064,11 @@
           <t>archive</t>
         </is>
       </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>open the camera</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -900,6 +1081,11 @@
           <t>archive</t>
         </is>
       </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>open that archived chat</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -912,6 +1098,11 @@
           <t>archive</t>
         </is>
       </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>go to chats</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -924,6 +1115,11 @@
           <t>archive</t>
         </is>
       </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>go to calls</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -936,6 +1132,11 @@
           <t>archive</t>
         </is>
       </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>go to stories</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -948,6 +1149,11 @@
           <t>archive</t>
         </is>
       </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>go to settings</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -960,6 +1166,11 @@
           <t>archive</t>
         </is>
       </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>go to profile</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -972,6 +1183,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>search the call log</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -984,6 +1200,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>open the calls overflow menu</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -996,6 +1217,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>open notification profiles</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1008,6 +1234,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>open proxy status</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1020,6 +1251,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>delete the call log</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1032,6 +1268,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>show only missed calls</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1044,6 +1285,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>show all calls again</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1056,6 +1302,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>manage notification profiles</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1068,6 +1319,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>start a new call</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1080,6 +1336,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>go to chats</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1092,6 +1353,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>stay on calls</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1104,6 +1370,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>go to stories</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1116,6 +1387,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>go to settings</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1128,6 +1404,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>go to profile</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -1140,6 +1421,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>call back or open call details</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1152,6 +1438,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>leave call search</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -1164,6 +1455,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>empty the search field</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1176,6 +1472,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>cancel multi-select</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1188,6 +1489,11 @@
           <t>calls</t>
         </is>
       </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>delete selected call entries</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1200,6 +1506,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>search stories</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -1212,6 +1523,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>open story privacy and more</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1224,6 +1540,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>open archived stories</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -1236,6 +1557,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>choose who can see stories</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1248,6 +1574,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>open notification profiles</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -1260,6 +1591,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>open proxy status</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1272,6 +1608,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>capture or create a story</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -1284,6 +1625,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>go to chats</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1296,6 +1642,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>go to calls</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -1308,6 +1659,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>stay on stories</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -1320,6 +1676,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>go to settings</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -1332,6 +1693,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>go to profile</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -1344,6 +1710,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>add to or view your story</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -1356,6 +1727,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>open that person’s story</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -1368,6 +1744,11 @@
           <t>stories</t>
         </is>
       </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>leave story search</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -1380,6 +1761,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>search settings items</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -1392,6 +1778,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>reserved overflow (no items)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -1404,6 +1795,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>open edit profile</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -1416,6 +1812,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>open your username QR / link</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -1428,6 +1829,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>open account settings</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -1440,6 +1846,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>open linked devices</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -1452,6 +1863,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>open donations</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -1464,6 +1880,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>open appearance</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -1476,6 +1897,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>open chat settings</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -1488,6 +1914,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>open story privacy</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -1500,6 +1931,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>open notification settings</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -1512,6 +1948,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>open privacy settings</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -1524,6 +1965,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>open backups</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -1536,6 +1982,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>open data and storage</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -1548,6 +1999,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>open app update settings</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -1560,6 +2016,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>open payments</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -1572,6 +2033,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>open help</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -1584,6 +2050,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>open invite</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -1596,6 +2067,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>open experimental features</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -1608,6 +2084,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>open internal tools</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -1620,6 +2101,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>open backup repair or renewal</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -1632,6 +2118,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>go to chats</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -1644,6 +2135,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>go to calls</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -1656,6 +2152,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>go to stories</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -1668,6 +2169,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>stay on settings</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -1680,6 +2186,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>go to profile</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -1692,6 +2203,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>leave settings search</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -1704,6 +2220,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>empty the search field</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -1716,6 +2237,11 @@
           <t>settings</t>
         </is>
       </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>open the matching settings screen</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -1728,6 +2254,11 @@
           <t>profile</t>
         </is>
       </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>reserved overflow</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -1740,6 +2271,11 @@
           <t>profile</t>
         </is>
       </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>go to chats</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -1752,6 +2288,11 @@
           <t>profile</t>
         </is>
       </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>go to calls</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -1764,6 +2305,11 @@
           <t>profile</t>
         </is>
       </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>go to stories</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -1776,6 +2322,11 @@
           <t>profile</t>
         </is>
       </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>go to settings</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -1788,6 +2339,11 @@
           <t>profile</t>
         </is>
       </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>stay on profile</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -1800,6 +2356,11 @@
           <t>profile</t>
         </is>
       </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>change or view your photo</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -1812,6 +2373,11 @@
           <t>profile</t>
         </is>
       </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>edit name, about, or username</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -1824,6 +2390,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>leave the thread</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -1836,6 +2407,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>open conversation settings</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -1848,6 +2424,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>start a voice call</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -1860,6 +2441,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>start a video call</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -1872,6 +2458,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>open thread actions</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -1884,6 +2475,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>search messages in this chat</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -1896,6 +2492,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>open shared media</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -1908,6 +2509,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>open chat or group settings</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -1920,6 +2526,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>add a home-screen shortcut</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -1932,6 +2543,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>open this chat in a bubble</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -1944,6 +2560,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>export the chat</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -1956,6 +2577,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>apply text formatting</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -1968,6 +2594,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>bold selected text</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -1980,6 +2611,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>italicize selected text</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -1992,6 +2628,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>strike selected text</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -2004,6 +2645,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>make selected text monospace</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -2016,6 +2662,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>hide selected text as a spoiler</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -2028,6 +2679,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>remove formatting</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -2040,6 +2696,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>change the disappear timer</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -2052,6 +2713,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>turn disappearing messages on</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -2064,6 +2730,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>mute this chat</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -2076,6 +2747,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>unmute this chat</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -2088,6 +2764,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>save this person as a contact</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -2100,6 +2781,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>open the attachment keyboard</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -2112,6 +2798,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>take a photo or video to send</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -2124,6 +2815,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>open the emoji keyboard</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -2136,6 +2832,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>open stickers</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -2148,6 +2849,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>open GIFs</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -2160,6 +2866,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>record a voice message</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -2172,6 +2883,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>send the composed message</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -2184,6 +2900,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>attach from the gallery</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -2196,6 +2917,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>attach a file</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -2208,6 +2934,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>share a location</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -2220,6 +2951,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>share a contact</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -2232,6 +2968,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>create a poll</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -2244,6 +2985,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>send a payment</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -2256,6 +3002,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>jump to the latest message</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -2268,6 +3019,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>allow messages from this sender</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -2280,6 +3036,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>block this sender</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -2292,6 +3053,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>delete the request or chat</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -2304,6 +3070,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>dismiss a safety or education prompt</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -2316,6 +3087,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>add or change a reaction</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -2328,6 +3104,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>quote this message</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -2340,6 +3121,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>copy message text</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -2352,6 +3138,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>forward the message</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -2364,6 +3155,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>star or unstar the message</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -2376,6 +3172,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>open message details</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -2388,6 +3189,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>enter multi-select on messages</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -2400,6 +3206,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>send a failed message again</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -2412,6 +3223,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>download media</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -2424,6 +3240,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>play a voice note</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -2436,6 +3257,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>pause a voice note</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -2448,6 +3274,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>open the previewed link</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -2460,6 +3291,11 @@
           <t>conversation</t>
         </is>
       </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>show more on a special message</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -2472,6 +3308,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>return to the chat</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -2484,6 +3325,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>return to the composer</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -2496,6 +3342,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>start a voice call</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -2508,6 +3359,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>start a video call</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -2520,6 +3376,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>search this chat</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -2532,6 +3393,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>set the disappear timer</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -2544,6 +3410,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>mute or unmute</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -2556,6 +3427,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>set a custom sound</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -2568,6 +3444,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>change color or wallpaper</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -2580,6 +3461,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>open notification options</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -2592,6 +3478,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>block this person</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -2604,6 +3495,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>save the contact</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -2616,6 +3512,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>verify the safety number</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -2628,6 +3529,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>share this contact</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -2640,6 +3546,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>open a member</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -2652,6 +3563,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>leave the group</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -2664,6 +3580,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>invite people</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -2676,6 +3597,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>manage the invite link</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -2688,6 +3614,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>rename the group</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -2700,6 +3631,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>change the group photo</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -2712,6 +3648,11 @@
           <t>conversation settings</t>
         </is>
       </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>more group or contact actions</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -2724,6 +3665,11 @@
           <t>account</t>
         </is>
       </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -2736,6 +3682,11 @@
           <t>account</t>
         </is>
       </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>jump to privacy</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -2748,6 +3699,11 @@
           <t>account</t>
         </is>
       </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>edit your profile</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -2760,6 +3716,11 @@
           <t>account</t>
         </is>
       </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>start changing your number</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -2772,6 +3733,11 @@
           <t>account</t>
         </is>
       </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>create or change your PIN</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -2784,6 +3750,11 @@
           <t>account</t>
         </is>
       </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>turn registration lock on or off</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -2796,6 +3767,11 @@
           <t>account</t>
         </is>
       </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>export or review account data</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -2808,6 +3784,11 @@
           <t>account</t>
         </is>
       </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>start account deletion</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -2820,6 +3801,11 @@
           <t>account</t>
         </is>
       </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>open linked devices</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -2832,6 +3818,11 @@
           <t>account</t>
         </is>
       </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>export account information</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -2844,6 +3835,11 @@
           <t>change number</t>
         </is>
       </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>go to the next change-number step</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -2856,6 +3852,11 @@
           <t>export account data</t>
         </is>
       </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>finish or confirm export</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -2868,6 +3869,11 @@
           <t>linked devices</t>
         </is>
       </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -2880,6 +3886,11 @@
           <t>linked devices</t>
         </is>
       </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>start linking a device</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
@@ -2892,6 +3903,11 @@
           <t>linked devices</t>
         </is>
       </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>rename a linked device</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -2904,6 +3920,11 @@
           <t>linked devices</t>
         </is>
       </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>remove a linked device</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -2916,6 +3937,11 @@
           <t>link device intro</t>
         </is>
       </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>go to the QR scanner</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -2928,6 +3954,11 @@
           <t>link device QR</t>
         </is>
       </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>grant camera permission</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -2940,6 +3971,11 @@
           <t>link device finished</t>
         </is>
       </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>close the success sheet</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -2952,6 +3988,11 @@
           <t>edit device name</t>
         </is>
       </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>save the new name</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -2964,6 +4005,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -2976,6 +4022,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>start a recurring donation</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
@@ -2988,6 +4039,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>make a one-time donation</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -3000,6 +4056,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>pay with PayPal</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -3012,6 +4073,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>pay with a card</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -3024,6 +4090,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>pay by bank transfer</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -3036,6 +4107,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>pay with iDEAL</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -3048,6 +4124,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>go to the next checkout step</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -3060,6 +4141,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>confirm the payment</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -3072,6 +4158,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>close the thank-you sheet</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -3084,6 +4175,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>change or cancel a donation</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -3096,6 +4192,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>stop recurring donations</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -3108,6 +4209,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>redeem a gift badge</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -3120,6 +4226,11 @@
           <t>appearance</t>
         </is>
       </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -3132,6 +4243,11 @@
           <t>appearance</t>
         </is>
       </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>choose light, dark, or system</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -3144,6 +4260,11 @@
           <t>appearance</t>
         </is>
       </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>choose the app language</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
@@ -3156,6 +4277,11 @@
           <t>appearance</t>
         </is>
       </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>set default color and wallpaper</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -3168,6 +4294,11 @@
           <t>appearance</t>
         </is>
       </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>choose the launcher icon</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -3180,6 +4311,11 @@
           <t>appearance</t>
         </is>
       </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>use compact or full tabs</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -3192,6 +4328,11 @@
           <t>appearance</t>
         </is>
       </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>turn an appearance option on or off</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -3204,6 +4345,11 @@
           <t>chats settings</t>
         </is>
       </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -3216,6 +4362,11 @@
           <t>chats settings</t>
         </is>
       </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>open SMS-related options</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
@@ -3228,6 +4379,11 @@
           <t>chats settings</t>
         </is>
       </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>change enter-key and keyboard behavior</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -3240,6 +4396,11 @@
           <t>chats settings</t>
         </is>
       </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>manage chat folders</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -3252,6 +4413,11 @@
           <t>chats settings</t>
         </is>
       </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>open backups</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -3264,6 +4430,11 @@
           <t>chats settings</t>
         </is>
       </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>turn a chat option on or off</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -3276,6 +4447,11 @@
           <t>chat folders</t>
         </is>
       </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>make a new folder</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -3288,6 +4464,11 @@
           <t>chat folders</t>
         </is>
       </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>change folder name or members</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -3300,6 +4481,11 @@
           <t>chat folders</t>
         </is>
       </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>remove a folder</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -3312,6 +4498,11 @@
           <t>chat folders</t>
         </is>
       </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>save folder changes</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
@@ -3324,6 +4515,11 @@
           <t>chat folders education</t>
         </is>
       </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>dismiss the folders explainer</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -3336,6 +4532,11 @@
           <t>stories privacy</t>
         </is>
       </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -3348,6 +4549,11 @@
           <t>stories privacy</t>
         </is>
       </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>edit who can see My Story</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -3360,6 +4566,11 @@
           <t>stories privacy</t>
         </is>
       </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>create a custom story</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -3372,6 +4583,11 @@
           <t>stories privacy</t>
         </is>
       </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>choose viewers</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -3384,6 +4600,11 @@
           <t>stories privacy</t>
         </is>
       </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>share with all connections</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
@@ -3396,6 +4617,11 @@
           <t>stories privacy</t>
         </is>
       </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>hide a story from someone</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -3408,6 +4634,11 @@
           <t>stories privacy</t>
         </is>
       </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>delete a custom story</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -3420,6 +4651,11 @@
           <t>stories privacy</t>
         </is>
       </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>save viewer changes</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -3432,6 +4668,11 @@
           <t>notifications</t>
         </is>
       </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
@@ -3444,6 +4685,11 @@
           <t>notifications</t>
         </is>
       </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>enable or disable an alert type</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -3456,6 +4702,11 @@
           <t>notifications</t>
         </is>
       </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>open profiles</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
@@ -3468,6 +4719,11 @@
           <t>notifications</t>
         </is>
       </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>configure message alerts</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -3480,6 +4736,11 @@
           <t>notifications</t>
         </is>
       </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>configure call alerts</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
@@ -3492,6 +4753,11 @@
           <t>notifications</t>
         </is>
       </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>choose when to notify</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -3504,6 +4770,11 @@
           <t>notification profiles</t>
         </is>
       </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>allow people through a profile</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
@@ -3516,6 +4787,11 @@
           <t>notification profiles</t>
         </is>
       </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>save the profile</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -3528,6 +4804,11 @@
           <t>turn on notifications sheet</t>
         </is>
       </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>open system notification settings</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -3540,6 +4821,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -3552,6 +4838,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>open the blocked list</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
@@ -3564,6 +4855,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>set the default timer</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -3576,6 +4872,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>open screen lock and related options</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -3588,6 +4889,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>require unlock to open Signal</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -3600,6 +4906,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>choose when the lock applies</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
@@ -3612,6 +4923,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>request incognito IME</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -3624,6 +4940,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>require PIN to re-register</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
@@ -3636,6 +4957,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>open advanced privacy</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -3648,6 +4974,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>control who sees your number</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
@@ -3660,6 +4991,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>open story privacy</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -3672,6 +5008,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>require unlock for payments</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -3684,6 +5025,11 @@
           <t>expire timer</t>
         </is>
       </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>save the timer</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -3696,6 +5042,11 @@
           <t>privacy</t>
         </is>
       </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>turn a privacy option on or off</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
@@ -3708,6 +5059,11 @@
           <t>backups settings</t>
         </is>
       </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -3720,6 +5076,11 @@
           <t>backups settings</t>
         </is>
       </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>pick local or remote backup</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
@@ -3732,6 +5093,11 @@
           <t>backups settings</t>
         </is>
       </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>start turning backups on</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -3744,6 +5110,11 @@
           <t>backups settings</t>
         </is>
       </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>open backup details</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
@@ -3756,6 +5127,11 @@
           <t>backups settings</t>
         </is>
       </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>start a restore</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -3768,6 +5144,11 @@
           <t>backups settings</t>
         </is>
       </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>open backups education</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
@@ -3780,6 +5161,11 @@
           <t>backups settings</t>
         </is>
       </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>run or schedule a backup</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -3792,6 +5178,11 @@
           <t>backups education</t>
         </is>
       </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>go to the next education step</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
@@ -3804,6 +5195,11 @@
           <t>backups type</t>
         </is>
       </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>choose a backup plan</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -3816,6 +5212,11 @@
           <t>backups type</t>
         </is>
       </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>confirm the plan</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
@@ -3828,6 +5229,11 @@
           <t>backups key education</t>
         </is>
       </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>go to record the key</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -3840,6 +5246,11 @@
           <t>backups record key</t>
         </is>
       </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>copy the recovery key</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
@@ -3852,6 +5263,11 @@
           <t>backups record key</t>
         </is>
       </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>share the recovery key</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -3864,6 +5280,11 @@
           <t>backups record key</t>
         </is>
       </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>confirm the key is stored</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
@@ -3876,6 +5297,11 @@
           <t>backups record key</t>
         </is>
       </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>go to verify the key</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -3888,6 +5314,11 @@
           <t>backups verify key</t>
         </is>
       </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>check the typed key</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
@@ -3900,6 +5331,11 @@
           <t>backups enter key</t>
         </is>
       </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>submit a recovery key</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -3912,6 +5348,11 @@
           <t>backups confirm key</t>
         </is>
       </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>accept the key</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
@@ -3924,6 +5365,11 @@
           <t>backup setup complete</t>
         </is>
       </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>close the success sheet</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -3936,6 +5382,11 @@
           <t>backup upsell</t>
         </is>
       </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>start a paid backup plan</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
@@ -3948,6 +5399,11 @@
           <t>media backups off</t>
         </is>
       </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>re-enable media backups</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -3960,6 +5416,11 @@
           <t>backup alert</t>
         </is>
       </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>dismiss a backup alert</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
@@ -3972,6 +5433,11 @@
           <t>recovery key warning</t>
         </is>
       </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>dismiss the warning</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -3984,6 +5450,11 @@
           <t>recovery key warning</t>
         </is>
       </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>proceed despite the warning</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
@@ -3996,6 +5467,11 @@
           <t>archive restore banner</t>
         </is>
       </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>retry a failed restore</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -4008,6 +5484,11 @@
           <t>upgrade media backup</t>
         </is>
       </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>upgrade to enable media backup</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -4020,6 +5501,11 @@
           <t>upgrade optimized storage</t>
         </is>
       </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>upgrade for optimized storage</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -4032,6 +5518,11 @@
           <t>data and storage</t>
         </is>
       </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
@@ -4044,6 +5535,11 @@
           <t>data and storage</t>
         </is>
       </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>review and free storage</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -4056,6 +5552,11 @@
           <t>data and storage</t>
         </is>
       </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>set sent media quality</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
@@ -4068,6 +5569,11 @@
           <t>data and storage</t>
         </is>
       </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>pick standard or high quality</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -4080,6 +5586,11 @@
           <t>data and storage</t>
         </is>
       </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>set call data use</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
@@ -4092,6 +5603,11 @@
           <t>data and storage</t>
         </is>
       </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>configure a proxy</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -4104,6 +5620,11 @@
           <t>data and storage</t>
         </is>
       </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>turn a storage option on or off</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
@@ -4116,6 +5637,11 @@
           <t>help</t>
         </is>
       </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -4128,6 +5654,11 @@
           <t>help</t>
         </is>
       </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>open support articles</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
@@ -4140,6 +5671,11 @@
           <t>help</t>
         </is>
       </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>start a support request</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -4152,6 +5688,11 @@
           <t>help</t>
         </is>
       </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>show or copy the app version</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
@@ -4164,6 +5705,11 @@
           <t>help</t>
         </is>
       </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>submit a debug log</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -4176,6 +5722,11 @@
           <t>help</t>
         </is>
       </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>open open-source licenses</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
@@ -4188,6 +5739,11 @@
           <t>help</t>
         </is>
       </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>open terms and privacy policy</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -4200,6 +5756,11 @@
           <t>help</t>
         </is>
       </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>go to the next help step</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
@@ -4212,6 +5773,11 @@
           <t>debug log</t>
         </is>
       </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>upload the debug log</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -4224,6 +5790,11 @@
           <t>invite</t>
         </is>
       </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
@@ -4236,6 +5807,11 @@
           <t>invite</t>
         </is>
       </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>share an invite link</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -4248,6 +5824,11 @@
           <t>invite</t>
         </is>
       </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>invite by SMS</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
@@ -4260,6 +5841,11 @@
           <t>labs</t>
         </is>
       </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -4272,6 +5858,11 @@
           <t>labs</t>
         </is>
       </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>turn an experimental flag on or off</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
@@ -4284,6 +5875,11 @@
           <t>internal</t>
         </is>
       </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -4296,6 +5892,11 @@
           <t>internal</t>
         </is>
       </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>open an internal tool</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
@@ -4308,6 +5909,11 @@
           <t>internal sqlite</t>
         </is>
       </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>run a debug query</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -4320,6 +5926,11 @@
           <t>internal donor</t>
         </is>
       </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>apply a test donor state</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
@@ -4332,6 +5943,11 @@
           <t>internal donations</t>
         </is>
       </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>save a test donation state</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -4344,6 +5960,11 @@
           <t>welcome</t>
         </is>
       </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>start new registration</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
@@ -4356,6 +5977,11 @@
           <t>welcome</t>
         </is>
       </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>restore or transfer an account</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -4368,6 +5994,11 @@
           <t>welcome</t>
         </is>
       </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>go to the next welcome step</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
@@ -4380,6 +6011,11 @@
           <t>phone number</t>
         </is>
       </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>return to welcome</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -4392,6 +6028,11 @@
           <t>phone number</t>
         </is>
       </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>pick a country code</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
@@ -4404,6 +6045,11 @@
           <t>phone number</t>
         </is>
       </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>request a verification code</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -4416,6 +6062,11 @@
           <t>country picker</t>
         </is>
       </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>return to the phone screen</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
@@ -4428,6 +6079,11 @@
           <t>country picker</t>
         </is>
       </c>
+      <c r="C331" s="3" t="inlineStr">
+        <is>
+          <t>select that country</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -4440,6 +6096,11 @@
           <t>verification code</t>
         </is>
       </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>return to the phone screen</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
@@ -4452,6 +6113,11 @@
           <t>verification code</t>
         </is>
       </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>request a new SMS code</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -4464,6 +6130,11 @@
           <t>verification code</t>
         </is>
       </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>request a voice code</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
@@ -4476,6 +6147,11 @@
           <t>verification code</t>
         </is>
       </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>submit the code</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -4488,6 +6164,11 @@
           <t>captcha</t>
         </is>
       </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>finish the captcha</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
@@ -4500,6 +6181,11 @@
           <t>PIN create</t>
         </is>
       </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>go back in registration</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -4512,6 +6198,11 @@
           <t>PIN create</t>
         </is>
       </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>save the new PIN</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
@@ -4524,6 +6215,11 @@
           <t>PIN create</t>
         </is>
       </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>skip creating a PIN</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -4536,6 +6232,11 @@
           <t>PIN entry</t>
         </is>
       </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>go back in registration</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
@@ -4548,6 +6249,11 @@
           <t>PIN entry</t>
         </is>
       </c>
+      <c r="C341" s="3" t="inlineStr">
+        <is>
+          <t>submit the PIN</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -4560,6 +6266,11 @@
           <t>PIN entry</t>
         </is>
       </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>start PIN recovery</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
@@ -4572,6 +6283,11 @@
           <t>create profile</t>
         </is>
       </c>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>go back in registration</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -4584,6 +6300,11 @@
           <t>create profile</t>
         </is>
       </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>set a profile photo</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
@@ -4596,6 +6317,11 @@
           <t>create profile</t>
         </is>
       </c>
+      <c r="C345" s="3" t="inlineStr">
+        <is>
+          <t>save the profile</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -4608,6 +6334,11 @@
           <t>create profile</t>
         </is>
       </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>skip profile setup</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
@@ -4620,6 +6351,11 @@
           <t>add username</t>
         </is>
       </c>
+      <c r="C347" s="3" t="inlineStr">
+        <is>
+          <t>go back in registration</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -4632,6 +6368,11 @@
           <t>add username</t>
         </is>
       </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>save the username</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
@@ -4644,6 +6385,11 @@
           <t>add username</t>
         </is>
       </c>
+      <c r="C349" s="3" t="inlineStr">
+        <is>
+          <t>skip username setup</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -4656,6 +6402,11 @@
           <t>permissions</t>
         </is>
       </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>go back in registration</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
@@ -4668,6 +6419,11 @@
           <t>permissions</t>
         </is>
       </c>
+      <c r="C351" s="3" t="inlineStr">
+        <is>
+          <t>grant contacts or phone permissions</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -4680,6 +6436,11 @@
           <t>permissions</t>
         </is>
       </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>skip permissions</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
@@ -4692,6 +6453,11 @@
           <t>allow notifications</t>
         </is>
       </c>
+      <c r="C353" s="3" t="inlineStr">
+        <is>
+          <t>go back in registration</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -4704,6 +6470,11 @@
           <t>allow notifications</t>
         </is>
       </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>request notification permission</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
@@ -4716,6 +6487,11 @@
           <t>allow notifications</t>
         </is>
       </c>
+      <c r="C355" s="3" t="inlineStr">
+        <is>
+          <t>skip notifications</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -4728,6 +6504,11 @@
           <t>discoverability</t>
         </is>
       </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>go back in registration</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
@@ -4740,6 +6521,11 @@
           <t>discoverability</t>
         </is>
       </c>
+      <c r="C357" s="3" t="inlineStr">
+        <is>
+          <t>save who can find you</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -4752,6 +6538,11 @@
           <t>account locked</t>
         </is>
       </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>leave the locked screen</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
@@ -4764,6 +6555,11 @@
           <t>account locked</t>
         </is>
       </c>
+      <c r="C359" s="3" t="inlineStr">
+        <is>
+          <t>explain why the account is locked</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -4776,6 +6572,11 @@
           <t>AEP entry</t>
         </is>
       </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>submit the account entropy / recovery key</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
@@ -4788,6 +6589,11 @@
           <t>AEP entry</t>
         </is>
       </c>
+      <c r="C361" s="3" t="inlineStr">
+        <is>
+          <t>continue after the key</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -4800,6 +6606,11 @@
           <t>Signal login info</t>
         </is>
       </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>accept login information</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
@@ -4812,6 +6623,11 @@
           <t>Signal login info</t>
         </is>
       </c>
+      <c r="C363" s="3" t="inlineStr">
+        <is>
+          <t>skip extra login info</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -4824,6 +6640,11 @@
           <t>Signal login payment</t>
         </is>
       </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>continue a login payment step</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
@@ -4836,6 +6657,11 @@
           <t>grant permissions</t>
         </is>
       </c>
+      <c r="C365" s="3" t="inlineStr">
+        <is>
+          <t>go back</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -4848,6 +6674,11 @@
           <t>grant permissions</t>
         </is>
       </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>request remaining permissions</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
@@ -4860,6 +6691,11 @@
           <t>restore method</t>
         </is>
       </c>
+      <c r="C367" s="3" t="inlineStr">
+        <is>
+          <t>return to welcome</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -4872,6 +6708,11 @@
           <t>restore method</t>
         </is>
       </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>restore from a Signal backup</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
@@ -4884,6 +6725,11 @@
           <t>restore method</t>
         </is>
       </c>
+      <c r="C369" s="3" t="inlineStr">
+        <is>
+          <t>restore from a local file</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -4896,6 +6742,11 @@
           <t>restore method</t>
         </is>
       </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>start device transfer</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
@@ -4908,6 +6759,11 @@
           <t>restore method</t>
         </is>
       </c>
+      <c r="C371" s="3" t="inlineStr">
+        <is>
+          <t>register with an empty account</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -4920,6 +6776,11 @@
           <t>enter backup key</t>
         </is>
       </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>return to restore method</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
@@ -4932,6 +6793,11 @@
           <t>enter backup key</t>
         </is>
       </c>
+      <c r="C373" s="3" t="inlineStr">
+        <is>
+          <t>submit the backup key</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -4944,6 +6810,11 @@
           <t>restore via QR</t>
         </is>
       </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>leave the QR restore camera</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
@@ -4956,6 +6827,11 @@
           <t>restore via QR</t>
         </is>
       </c>
+      <c r="C375" s="3" t="inlineStr">
+        <is>
+          <t>generate or scan the QR again</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -4968,6 +6844,11 @@
           <t>no backup</t>
         </is>
       </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>return to restore options</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
@@ -4980,6 +6861,11 @@
           <t>no backup</t>
         </is>
       </c>
+      <c r="C377" s="3" t="inlineStr">
+        <is>
+          <t>register without restoring</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -4992,6 +6878,11 @@
           <t>remote restore</t>
         </is>
       </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>leave remote restore</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
@@ -5004,6 +6895,11 @@
           <t>remote restore</t>
         </is>
       </c>
+      <c r="C379" s="3" t="inlineStr">
+        <is>
+          <t>stop the restore</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -5016,6 +6912,11 @@
           <t>remote restore</t>
         </is>
       </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>skip waiting for media</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
@@ -5028,6 +6929,11 @@
           <t>remote restore</t>
         </is>
       </c>
+      <c r="C381" s="3" t="inlineStr">
+        <is>
+          <t>proceed after restore</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -5040,6 +6946,11 @@
           <t>local backup</t>
         </is>
       </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>return to restore method</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="3" t="inlineStr">
@@ -5052,6 +6963,11 @@
           <t>local backup</t>
         </is>
       </c>
+      <c r="C383" s="3" t="inlineStr">
+        <is>
+          <t>pick a backup file</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -5064,6 +6980,11 @@
           <t>local backup</t>
         </is>
       </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>start restoring that file</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="3" t="inlineStr">
@@ -5076,6 +6997,11 @@
           <t>local backup sheet</t>
         </is>
       </c>
+      <c r="C385" s="3" t="inlineStr">
+        <is>
+          <t>confirm the chosen file</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -5088,6 +7014,11 @@
           <t>local backup instructions</t>
         </is>
       </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>dismiss restore instructions</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
@@ -5100,6 +7031,11 @@
           <t>local backup key</t>
         </is>
       </c>
+      <c r="C387" s="3" t="inlineStr">
+        <is>
+          <t>submit the local backup key</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -5112,6 +7048,11 @@
           <t>local V1 passphrase</t>
         </is>
       </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>unlock a V1 backup</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
@@ -5124,6 +7065,11 @@
           <t>link account</t>
         </is>
       </c>
+      <c r="C389" s="3" t="inlineStr">
+        <is>
+          <t>refresh the link QR</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -5136,6 +7082,11 @@
           <t>link account</t>
         </is>
       </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>leave link-account</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="3" t="inlineStr">
@@ -5148,6 +7099,11 @@
           <t>device transfer setup</t>
         </is>
       </c>
+      <c r="C391" s="3" t="inlineStr">
+        <is>
+          <t>leave transfer setup</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -5160,6 +7116,11 @@
           <t>device transfer setup</t>
         </is>
       </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>start or confirm transfer</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="3" t="inlineStr">
@@ -5172,6 +7133,11 @@
           <t>device transfer setup</t>
         </is>
       </c>
+      <c r="C393" s="3" t="inlineStr">
+        <is>
+          <t>abort setup</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -5184,6 +7150,11 @@
           <t>device transfer setup</t>
         </is>
       </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>retry a failed setup</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="3" t="inlineStr">
@@ -5196,6 +7167,11 @@
           <t>device transfer instructions</t>
         </is>
       </c>
+      <c r="C395" s="3" t="inlineStr">
+        <is>
+          <t>go to the next transfer step</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -5208,6 +7184,11 @@
           <t>device transfer progress</t>
         </is>
       </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>stop an in-progress transfer</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="3" t="inlineStr">
@@ -5220,6 +7201,11 @@
           <t>device transfer progress</t>
         </is>
       </c>
+      <c r="C397" s="3" t="inlineStr">
+        <is>
+          <t>retry a failed transfer</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -5232,6 +7218,11 @@
           <t>device transfer complete</t>
         </is>
       </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>finish transfer</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="3" t="inlineStr">
@@ -5244,6 +7235,11 @@
           <t>message sync</t>
         </is>
       </c>
+      <c r="C399" s="3" t="inlineStr">
+        <is>
+          <t>finish or skip message sync</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -5256,6 +7252,11 @@
           <t>prepare device</t>
         </is>
       </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>mark this device ready to transfer</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="3" t="inlineStr">
@@ -5268,6 +7269,11 @@
           <t>transfer account</t>
         </is>
       </c>
+      <c r="C401" s="3" t="inlineStr">
+        <is>
+          <t>start sending the account</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -5280,6 +7286,11 @@
           <t>story viewer</t>
         </is>
       </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>close the story</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="3" t="inlineStr">
@@ -5292,6 +7303,11 @@
           <t>story viewer</t>
         </is>
       </c>
+      <c r="C403" s="3" t="inlineStr">
+        <is>
+          <t>open story actions</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -5304,6 +7320,11 @@
           <t>story viewer</t>
         </is>
       </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>reply to the story</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="3" t="inlineStr">
@@ -5316,6 +7337,11 @@
           <t>story viewer</t>
         </is>
       </c>
+      <c r="C405" s="3" t="inlineStr">
+        <is>
+          <t>react to the story</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -5328,6 +7354,11 @@
           <t>story viewer</t>
         </is>
       </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>see who viewed the story</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="3" t="inlineStr">
@@ -5340,6 +7371,11 @@
           <t>story viewer</t>
         </is>
       </c>
+      <c r="C407" s="3" t="inlineStr">
+        <is>
+          <t>forward the story</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -5352,6 +7388,11 @@
           <t>story viewer</t>
         </is>
       </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>delete your story</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
@@ -5364,6 +7405,11 @@
           <t>story viewer</t>
         </is>
       </c>
+      <c r="C409" s="3" t="inlineStr">
+        <is>
+          <t>open story info</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -5376,6 +7422,11 @@
           <t>story viewer</t>
         </is>
       </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>pause playback</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
@@ -5388,6 +7439,11 @@
           <t>story archive</t>
         </is>
       </c>
+      <c r="C411" s="3" t="inlineStr">
+        <is>
+          <t>leave the archive</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -5400,6 +7456,11 @@
           <t>story archive</t>
         </is>
       </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>restore a story from the archive</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="3" t="inlineStr">
@@ -5412,6 +7473,11 @@
           <t>story archive</t>
         </is>
       </c>
+      <c r="C413" s="3" t="inlineStr">
+        <is>
+          <t>play an archived story</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -5424,6 +7490,11 @@
           <t>camera</t>
         </is>
       </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>leave the camera</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
@@ -5436,6 +7507,11 @@
           <t>camera</t>
         </is>
       </c>
+      <c r="C415" s="3" t="inlineStr">
+        <is>
+          <t>switch front and rear cameras</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -5448,6 +7524,11 @@
           <t>camera</t>
         </is>
       </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>toggle flash</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="3" t="inlineStr">
@@ -5460,6 +7541,11 @@
           <t>camera</t>
         </is>
       </c>
+      <c r="C417" s="3" t="inlineStr">
+        <is>
+          <t>take a photo or start/stop video</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -5472,6 +7558,11 @@
           <t>camera</t>
         </is>
       </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>pick existing media</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
@@ -5484,6 +7575,11 @@
           <t>camera</t>
         </is>
       </c>
+      <c r="C419" s="3" t="inlineStr">
+        <is>
+          <t>switch photo and video mode</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -5496,6 +7592,11 @@
           <t>media send</t>
         </is>
       </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>go to the review screen</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="3" t="inlineStr">
@@ -5508,6 +7609,11 @@
           <t>media send</t>
         </is>
       </c>
+      <c r="C421" s="3" t="inlineStr">
+        <is>
+          <t>send the selected media</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -5520,6 +7626,11 @@
           <t>media send</t>
         </is>
       </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>add a caption</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
@@ -5532,6 +7643,11 @@
           <t>media send</t>
         </is>
       </c>
+      <c r="C423" s="3" t="inlineStr">
+        <is>
+          <t>crop the image</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -5544,6 +7660,11 @@
           <t>media send</t>
         </is>
       </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>draw on the image</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
@@ -5556,6 +7677,11 @@
           <t>media send</t>
         </is>
       </c>
+      <c r="C425" s="3" t="inlineStr">
+        <is>
+          <t>add text on the image</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -5568,6 +7694,11 @@
           <t>media send</t>
         </is>
       </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>blur faces or regions</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="3" t="inlineStr">
@@ -5580,6 +7711,11 @@
           <t>media send</t>
         </is>
       </c>
+      <c r="C427" s="3" t="inlineStr">
+        <is>
+          <t>undo the last edit</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -5592,6 +7728,11 @@
           <t>media send</t>
         </is>
       </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>change send quality</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="3" t="inlineStr">
@@ -5604,6 +7745,11 @@
           <t>media preview</t>
         </is>
       </c>
+      <c r="C429" s="3" t="inlineStr">
+        <is>
+          <t>close the preview</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -5616,6 +7762,11 @@
           <t>media preview</t>
         </is>
       </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>edit this media</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="3" t="inlineStr">
@@ -5628,6 +7779,11 @@
           <t>media preview</t>
         </is>
       </c>
+      <c r="C431" s="3" t="inlineStr">
+        <is>
+          <t>save to the device</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -5640,6 +7796,11 @@
           <t>media preview</t>
         </is>
       </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>delete this media</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
@@ -5652,6 +7813,11 @@
           <t>media preview</t>
         </is>
       </c>
+      <c r="C433" s="3" t="inlineStr">
+        <is>
+          <t>share this media</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -5664,6 +7830,11 @@
           <t>media preview</t>
         </is>
       </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>more preview actions</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="3" t="inlineStr">
@@ -5676,6 +7847,11 @@
           <t>media gallery</t>
         </is>
       </c>
+      <c r="C435" s="3" t="inlineStr">
+        <is>
+          <t>toggle selection on an item</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -5688,6 +7864,11 @@
           <t>media gallery</t>
         </is>
       </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>send the selected items</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="3" t="inlineStr">
@@ -5700,6 +7881,11 @@
           <t>in call</t>
         </is>
       </c>
+      <c r="C437" s="3" t="inlineStr">
+        <is>
+          <t>leave call UI if allowed</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -5712,6 +7898,11 @@
           <t>in call</t>
         </is>
       </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>more in-call actions</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
@@ -5724,6 +7915,11 @@
           <t>in call</t>
         </is>
       </c>
+      <c r="C439" s="3" t="inlineStr">
+        <is>
+          <t>show the participant list</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -5736,6 +7932,11 @@
           <t>in call</t>
         </is>
       </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>mute or unmute the mic</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="3" t="inlineStr">
@@ -5748,6 +7949,11 @@
           <t>in call</t>
         </is>
       </c>
+      <c r="C441" s="3" t="inlineStr">
+        <is>
+          <t>turn the camera on or off</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -5760,6 +7966,11 @@
           <t>in call</t>
         </is>
       </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>toggle speakerphone</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
@@ -5772,6 +7983,11 @@
           <t>in call</t>
         </is>
       </c>
+      <c r="C443" s="3" t="inlineStr">
+        <is>
+          <t>pick speaker, earpiece, or headset</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -5784,6 +8000,11 @@
           <t>in call</t>
         </is>
       </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>ring remaining group members</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
@@ -5796,6 +8017,11 @@
           <t>in call</t>
         </is>
       </c>
+      <c r="C445" s="3" t="inlineStr">
+        <is>
+          <t>open call effects</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -5808,6 +8034,11 @@
           <t>in call</t>
         </is>
       </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>share the screen</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
@@ -5820,6 +8051,11 @@
           <t>in call</t>
         </is>
       </c>
+      <c r="C447" s="3" t="inlineStr">
+        <is>
+          <t>end the call</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -5832,6 +8068,11 @@
           <t>incoming call</t>
         </is>
       </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>accept the call</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="3" t="inlineStr">
@@ -5844,6 +8085,11 @@
           <t>incoming call</t>
         </is>
       </c>
+      <c r="C449" s="3" t="inlineStr">
+        <is>
+          <t>reject the call</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -5856,6 +8102,11 @@
           <t>pre join</t>
         </is>
       </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>join the call or link</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="3" t="inlineStr">
@@ -5868,6 +8119,11 @@
           <t>pre join</t>
         </is>
       </c>
+      <c r="C451" s="3" t="inlineStr">
+        <is>
+          <t>leave pre-join</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -5880,6 +8136,11 @@
           <t>call quality</t>
         </is>
       </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>go to the next feedback step</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
@@ -5892,6 +8153,11 @@
           <t>call quality</t>
         </is>
       </c>
+      <c r="C453" s="3" t="inlineStr">
+        <is>
+          <t>send call-quality feedback</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -5904,6 +8170,11 @@
           <t>call quality</t>
         </is>
       </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>describe another problem</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
@@ -5916,6 +8187,11 @@
           <t>call quality diagnostics</t>
         </is>
       </c>
+      <c r="C455" s="3" t="inlineStr">
+        <is>
+          <t>close diagnostics</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -5928,6 +8204,11 @@
           <t>call links</t>
         </is>
       </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>make a new call link</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
@@ -5940,6 +8221,11 @@
           <t>call links</t>
         </is>
       </c>
+      <c r="C457" s="3" t="inlineStr">
+        <is>
+          <t>rename the call link</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -5952,6 +8238,11 @@
           <t>call links</t>
         </is>
       </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>share the call link</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="3" t="inlineStr">
@@ -5964,6 +8255,11 @@
           <t>call links</t>
         </is>
       </c>
+      <c r="C459" s="3" t="inlineStr">
+        <is>
+          <t>join via the link</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -5976,6 +8272,11 @@
           <t>call links</t>
         </is>
       </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>delete the call link</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="3" t="inlineStr">
@@ -5988,6 +8289,11 @@
           <t>edit call link name</t>
         </is>
       </c>
+      <c r="C461" s="3" t="inlineStr">
+        <is>
+          <t>save the new name</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -6000,6 +8306,11 @@
           <t>call links</t>
         </is>
       </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>let a waiting person join</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="3" t="inlineStr">
@@ -6012,6 +8323,11 @@
           <t>payments</t>
         </is>
       </c>
+      <c r="C463" s="3" t="inlineStr">
+        <is>
+          <t>return to settings</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -6024,6 +8340,11 @@
           <t>payments</t>
         </is>
       </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>more payment actions</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="3" t="inlineStr">
@@ -6036,6 +8357,11 @@
           <t>payments</t>
         </is>
       </c>
+      <c r="C465" s="3" t="inlineStr">
+        <is>
+          <t>create a payments account</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -6048,6 +8374,11 @@
           <t>payments</t>
         </is>
       </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>show how to receive funds</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="3" t="inlineStr">
@@ -6060,6 +8391,11 @@
           <t>payments</t>
         </is>
       </c>
+      <c r="C467" s="3" t="inlineStr">
+        <is>
+          <t>start a payment</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -6072,6 +8408,11 @@
           <t>payments</t>
         </is>
       </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>open a transaction</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="3" t="inlineStr">
@@ -6084,6 +8425,11 @@
           <t>payments</t>
         </is>
       </c>
+      <c r="C469" s="3" t="inlineStr">
+        <is>
+          <t>change display currency</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -6096,6 +8442,11 @@
           <t>payments</t>
         </is>
       </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>transfer out</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="3" t="inlineStr">
@@ -6108,6 +8459,11 @@
           <t>payments</t>
         </is>
       </c>
+      <c r="C471" s="3" t="inlineStr">
+        <is>
+          <t>view or confirm the phrase</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -6120,6 +8476,11 @@
           <t>payments</t>
         </is>
       </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>turn payments off</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
@@ -6132,6 +8493,11 @@
           <t>create payment</t>
         </is>
       </c>
+      <c r="C473" s="3" t="inlineStr">
+        <is>
+          <t>go to the next send step</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -6144,6 +8510,11 @@
           <t>create payment</t>
         </is>
       </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>send the payment</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="3" t="inlineStr">
@@ -6156,6 +8527,11 @@
           <t>create payment</t>
         </is>
       </c>
+      <c r="C475" s="3" t="inlineStr">
+        <is>
+          <t>confirm the amount</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -6168,6 +8544,11 @@
           <t>edit note</t>
         </is>
       </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>save the payment note</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="3" t="inlineStr">
@@ -6180,6 +8561,11 @@
           <t>payments recovery</t>
         </is>
       </c>
+      <c r="C477" s="3" t="inlineStr">
+        <is>
+          <t>go to the next recovery step</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -6192,6 +8578,11 @@
           <t>payments recovery</t>
         </is>
       </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>continue the phrase flow</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="3" t="inlineStr">
@@ -6204,6 +8595,11 @@
           <t>payments recovery</t>
         </is>
       </c>
+      <c r="C479" s="3" t="inlineStr">
+        <is>
+          <t>confirm the phrase</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -6216,6 +8612,11 @@
           <t>payment info card</t>
         </is>
       </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>more info-card actions</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="3" t="inlineStr">
@@ -6228,6 +8629,11 @@
           <t>username link</t>
         </is>
       </c>
+      <c r="C481" s="3" t="inlineStr">
+        <is>
+          <t>return to profile</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -6240,6 +8646,11 @@
           <t>username link</t>
         </is>
       </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>share the username QR or link</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="3" t="inlineStr">
@@ -6252,6 +8663,11 @@
           <t>username link</t>
         </is>
       </c>
+      <c r="C483" s="3" t="inlineStr">
+        <is>
+          <t>change QR color</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -6264,6 +8680,11 @@
           <t>username link</t>
         </is>
       </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>reset the username link</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
@@ -6276,6 +8697,11 @@
           <t>username link</t>
         </is>
       </c>
+      <c r="C485" s="3" t="inlineStr">
+        <is>
+          <t>copy the username or link</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -6288,6 +8714,11 @@
           <t>username QR color</t>
         </is>
       </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>save the QR color</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
@@ -6300,6 +8731,11 @@
           <t>new ways to connect</t>
         </is>
       </c>
+      <c r="C487" s="3" t="inlineStr">
+        <is>
+          <t>dismiss the username explainer</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -6312,6 +8748,11 @@
           <t>find by</t>
         </is>
       </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>leave find-by</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
@@ -6324,6 +8765,11 @@
           <t>find by</t>
         </is>
       </c>
+      <c r="C489" s="3" t="inlineStr">
+        <is>
+          <t>search for that number or username</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -6336,6 +8782,11 @@
           <t>find by</t>
         </is>
       </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>run the lookup</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="3" t="inlineStr">
@@ -6348,6 +8799,11 @@
           <t>nickname</t>
         </is>
       </c>
+      <c r="C491" s="3" t="inlineStr">
+        <is>
+          <t>leave nickname edit</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -6360,6 +8816,11 @@
           <t>nickname</t>
         </is>
       </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>save the nickname and note</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
@@ -6372,6 +8833,11 @@
           <t>add to group</t>
         </is>
       </c>
+      <c r="C493" s="3" t="inlineStr">
+        <is>
+          <t>leave member picker</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -6384,6 +8850,11 @@
           <t>add to group</t>
         </is>
       </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>add the selected people</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
@@ -6396,6 +8867,11 @@
           <t>add members</t>
         </is>
       </c>
+      <c r="C495" s="3" t="inlineStr">
+        <is>
+          <t>confirm new members</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -6408,6 +8884,11 @@
           <t>create group</t>
         </is>
       </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>go to group name and photo</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
@@ -6420,6 +8901,11 @@
           <t>member label</t>
         </is>
       </c>
+      <c r="C497" s="3" t="inlineStr">
+        <is>
+          <t>save the member label</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -6432,6 +8918,11 @@
           <t>member label education</t>
         </is>
       </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>dismiss the explainer</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
@@ -6444,6 +8935,11 @@
           <t>member label about</t>
         </is>
       </c>
+      <c r="C499" s="3" t="inlineStr">
+        <is>
+          <t>save the about override</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -6456,6 +8952,11 @@
           <t>safety number</t>
         </is>
       </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>dismiss the safety-number sheet</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
@@ -6468,6 +8969,11 @@
           <t>safety number</t>
         </is>
       </c>
+      <c r="C501" s="3" t="inlineStr">
+        <is>
+          <t>open safety-number verification</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -6480,6 +8986,11 @@
           <t>safety number review</t>
         </is>
       </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>proceed after reviewing connections</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
@@ -6492,6 +9003,11 @@
           <t>verify automatically education</t>
         </is>
       </c>
+      <c r="C503" s="3" t="inlineStr">
+        <is>
+          <t>learn about automatic verification</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -6504,6 +9020,11 @@
           <t>encryption verified</t>
         </is>
       </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>dismiss verified status</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="3" t="inlineStr">
@@ -6516,6 +9037,11 @@
           <t>self verification failure</t>
         </is>
       </c>
+      <c r="C505" s="3" t="inlineStr">
+        <is>
+          <t>retry verification</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -6528,6 +9054,11 @@
           <t>self verification failure</t>
         </is>
       </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>close the failure sheet</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
@@ -6540,6 +9071,11 @@
           <t>sticker pack</t>
         </is>
       </c>
+      <c r="C507" s="3" t="inlineStr">
+        <is>
+          <t>install the pack</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -6552,6 +9088,11 @@
           <t>sticker pack</t>
         </is>
       </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>uninstall the pack</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
@@ -6564,6 +9105,11 @@
           <t>restore complete</t>
         </is>
       </c>
+      <c r="C509" s="3" t="inlineStr">
+        <is>
+          <t>dismiss restore-complete</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -6576,6 +9122,11 @@
           <t>terminated group</t>
         </is>
       </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>dismiss the ended-group sheet</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
@@ -6588,6 +9139,11 @@
           <t>relink devices</t>
         </is>
       </c>
+      <c r="C511" s="3" t="inlineStr">
+        <is>
+          <t>start relinking devices</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
@@ -6600,6 +9156,11 @@
           <t>safety tips</t>
         </is>
       </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>dismiss safety tips</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="3" t="inlineStr">
@@ -6612,6 +9173,11 @@
           <t>pin disappearing messages</t>
         </is>
       </c>
+      <c r="C513" s="3" t="inlineStr">
+        <is>
+          <t>dismiss the pin explainer</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -6624,6 +9190,11 @@
           <t>media no longer available</t>
         </is>
       </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>dismiss the missing-media sheet</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="3" t="inlineStr">
@@ -6636,6 +9207,11 @@
           <t>create poll</t>
         </is>
       </c>
+      <c r="C515" s="3" t="inlineStr">
+        <is>
+          <t>send the poll</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -6648,6 +9224,11 @@
           <t>poll votes</t>
         </is>
       </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>change or view a vote</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="3" t="inlineStr">
@@ -6660,6 +9241,11 @@
           <t>username share</t>
         </is>
       </c>
+      <c r="C517" s="3" t="inlineStr">
+        <is>
+          <t>open username share</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -6672,6 +9258,11 @@
           <t>username settings</t>
         </is>
       </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>reset username settings</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="3" t="inlineStr">
@@ -6684,6 +9275,11 @@
           <t>bank transfer mandate</t>
         </is>
       </c>
+      <c r="C519" s="3" t="inlineStr">
+        <is>
+          <t>accept the mandate</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -6696,6 +9292,11 @@
           <t>iDEAL details</t>
         </is>
       </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>submit iDEAL details</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="3" t="inlineStr">
@@ -6708,6 +9309,11 @@
           <t>bank transfer details</t>
         </is>
       </c>
+      <c r="C521" s="3" t="inlineStr">
+        <is>
+          <t>submit bank details</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -6720,6 +9326,11 @@
           <t>gateway selector</t>
         </is>
       </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>pay with the selected method</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
@@ -6732,6 +9343,11 @@
           <t>gateway selector</t>
         </is>
       </c>
+      <c r="C523" s="3" t="inlineStr">
+        <is>
+          <t>show more payment methods</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -6744,6 +9360,11 @@
           <t>donation pending</t>
         </is>
       </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>dismiss pending donation</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="3" t="inlineStr">
@@ -6756,6 +9377,11 @@
           <t>terminal donation</t>
         </is>
       </c>
+      <c r="C525" s="3" t="inlineStr">
+        <is>
+          <t>close the finished donation</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -6768,6 +9394,11 @@
           <t>change number wait</t>
         </is>
       </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>dismiss the wait sheet</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
@@ -6780,6 +9411,11 @@
           <t>device specific notification</t>
         </is>
       </c>
+      <c r="C527" s="3" t="inlineStr">
+        <is>
+          <t>skip extra notification setup</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -6792,6 +9428,11 @@
           <t>device specific notification</t>
         </is>
       </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>open system settings</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
@@ -6804,6 +9445,11 @@
           <t>delete sync education</t>
         </is>
       </c>
+      <c r="C529" s="3" t="inlineStr">
+        <is>
+          <t>dismiss delete-sync education</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
@@ -6816,6 +9462,11 @@
           <t>connectivity warning</t>
         </is>
       </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>open connectivity help</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
@@ -6828,6 +9479,11 @@
           <t>connectivity warning</t>
         </is>
       </c>
+      <c r="C531" s="3" t="inlineStr">
+        <is>
+          <t>hide the warning</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -6840,6 +9496,11 @@
           <t>clock skew</t>
         </is>
       </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>fix device time</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="3" t="inlineStr">
@@ -6852,6 +9513,11 @@
           <t>Device PIN education</t>
         </is>
       </c>
+      <c r="C533" s="3" t="inlineStr">
+        <is>
+          <t>dismiss PIN education</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -6864,6 +9530,11 @@
           <t>monthly donation canceled</t>
         </is>
       </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>restart a donation</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="3" t="inlineStr">
@@ -6876,6 +9547,11 @@
           <t>search filter</t>
         </is>
       </c>
+      <c r="C535" s="3" t="inlineStr">
+        <is>
+          <t>apply search filters</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
@@ -6888,6 +9564,11 @@
           <t>search filter</t>
         </is>
       </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>clear search filters</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="3" t="inlineStr">
@@ -6900,6 +9581,11 @@
           <t>Quick Restore info</t>
         </is>
       </c>
+      <c r="C537" s="3" t="inlineStr">
+        <is>
+          <t>dismiss QR-restore info</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -6912,6 +9598,11 @@
           <t>turn on notifications</t>
         </is>
       </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>enable notifications</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="3" t="inlineStr">
@@ -6924,6 +9615,11 @@
           <t>chats settings</t>
         </is>
       </c>
+      <c r="C539" s="3" t="inlineStr">
+        <is>
+          <t>upgrade a local backup</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -6936,6 +9632,11 @@
           <t>verify education</t>
         </is>
       </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>dismiss verification education</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="3" t="inlineStr">
@@ -6948,6 +9649,11 @@
           <t>dialog</t>
         </is>
       </c>
+      <c r="C541" s="3" t="inlineStr">
+        <is>
+          <t>accept the dialog action</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -6960,6 +9666,11 @@
           <t>dialog</t>
         </is>
       </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>close the dialog without the primary action</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="3" t="inlineStr">
@@ -6972,6 +9683,11 @@
           <t>dialog</t>
         </is>
       </c>
+      <c r="C543" s="3" t="inlineStr">
+        <is>
+          <t>acknowledge the dialog</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
@@ -6984,6 +9700,11 @@
           <t>dialog</t>
         </is>
       </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>cancel the dialog</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="3" t="inlineStr">
@@ -6996,9 +9717,14 @@
           <t>snackbar</t>
         </is>
       </c>
+      <c r="C545" s="3" t="inlineStr">
+        <is>
+          <t>undo or act on the snackbar</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B545"/>
+  <autoFilter ref="A1:C545"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>